--- a/todo-board.xlsx
+++ b/todo-board.xlsx
@@ -1,50 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akshay.kk\Documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{092B00B7-E393-4447-B367-C3622A84B481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3EFCFB70-D970-444D-99B4-1C50D7795775}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Tasks" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Activity log" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -70,21 +67,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -99,44 +88,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -164,31 +153,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -216,23 +188,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -244,136 +199,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -395,25 +394,223 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA28C552-969E-431A-9151-438A9F36A279}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J2"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.83203125" customWidth="1"/>
+    <col min="3" max="3" width="52.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Progress %</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Due date</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Created</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Last updated</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Colour</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>To do</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="J2" t="str">
+        <v>--p1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{611efef2-56e9-4a57-b83d-0b8cd251f5f4}" enabled="1" method="Privileged" siteId="{139f0669-cebb-42df-b9e3-415009ddb690}" contentBits="0" removed="0"/>
-</clbl:labelList>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Metric</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Total notes</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>To do</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>In progress</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Done</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Overall progress %</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Overdue</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Last saved</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="46.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Task ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Task</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Event</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Detail</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B2" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C2" t="str">
+        <v>(untitled)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Created</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/todo-board.xlsx
+++ b/todo-board.xlsx
@@ -450,7 +450,7 @@
         <v>T-0HFNF28</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v xml:space="preserve">Coveo RSP </v>
       </c>
       <c r="C2" t="str">
         <v/>
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E12"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -608,9 +608,179 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B3" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>C</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E3" t="str">
+        <v>C</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B4" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Co</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Co</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B5" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Cov</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Cov</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B6" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Cove</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Cove</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B7" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Coveo</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Coveo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B8" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C8" t="str">
+        <v xml:space="preserve">Coveo </v>
+      </c>
+      <c r="D8" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E8" t="str">
+        <v xml:space="preserve">Coveo </v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B9" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Coveo R</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Coveo R</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B10" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Coveo RS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Coveo RS</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B11" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Coveo RSP</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Coveo RSP</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-08-17 14:38</v>
+      </c>
+      <c r="B12" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C12" t="str">
+        <v xml:space="preserve">Coveo RSP </v>
+      </c>
+      <c r="D12" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E12" t="str">
+        <v xml:space="preserve">Coveo RSP </v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/todo-board.xlsx
+++ b/todo-board.xlsx
@@ -450,13 +450,13 @@
         <v>T-0HFNF28</v>
       </c>
       <c r="B2" t="str">
-        <v xml:space="preserve">Coveo RSP </v>
+        <v>Coveo RSP QPM Mail</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2" t="str">
-        <v>To do</v>
+        <v>In progress</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -471,7 +471,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>2026-08-17 14:38</v>
+        <v>2026-08-17 14:39</v>
       </c>
       <c r="J2" t="str">
         <v>--p1</v>
@@ -513,7 +513,7 @@
         <v>To do</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>In progress</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>Last saved</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-08-17 14:38</v>
+        <v>2026-08-17 14:39</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E29"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -778,9 +778,298 @@
         <v xml:space="preserve">Coveo RSP </v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B13" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Coveo RSP Q</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Coveo RSP Q</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B14" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Coveo RSP QP</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Coveo RSP QP</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B15" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Coveo RSP QPM</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Coveo RSP QPM</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B16" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C16" t="str">
+        <v xml:space="preserve">Coveo RSP QPM </v>
+      </c>
+      <c r="D16" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E16" t="str">
+        <v xml:space="preserve">Coveo RSP QPM </v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B17" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Coveo RSP QPM M</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Coveo RSP QPM M</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B18" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Coveo RSP QPM MA</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Coveo RSP QPM MA</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B19" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Coveo RSP QPM MAi</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Coveo RSP QPM MAi</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B20" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Coveo RSP QPM MAil</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Coveo RSP QPM MAil</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B21" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C21" t="str">
+        <v xml:space="preserve">Coveo RSP QPM MAil </v>
+      </c>
+      <c r="D21" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E21" t="str">
+        <v xml:space="preserve">Coveo RSP QPM MAil </v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B22" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Coveo RSP QPM MAil</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Coveo RSP QPM MAil</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B23" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Coveo RSP QPM MAi</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Coveo RSP QPM MAi</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B24" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Coveo RSP QPM MA</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Coveo RSP QPM MA</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B25" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Coveo RSP QPM M</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Coveo RSP QPM M</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B26" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Coveo RSP QPM Ma</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Coveo RSP QPM Ma</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B27" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Coveo RSP QPM Mai</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Coveo RSP QPM Mai</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B28" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Coveo RSP QPM Mail</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Title edited</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Coveo RSP QPM Mail</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2026-08-17 14:39</v>
+      </c>
+      <c r="B29" t="str">
+        <v>T-0HFNF28</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Coveo RSP QPM Mail</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Status changed</v>
+      </c>
+      <c r="E29" t="str">
+        <v>To do → In progress</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E29"/>
   </ignoredErrors>
 </worksheet>
 </file>